--- a/Result/profitability/2434.xlsx
+++ b/Result/profitability/2434.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07625000000000004</v>
+        <v>-0.15625</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.585000000000007</v>
+        <v>-14.62750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06625000000000003</v>
+        <v>-0.05125000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.213750000000008</v>
+        <v>-14.91375000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.003750000000000038</v>
+        <v>-0.11625</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.400000000000007</v>
+        <v>-14.71125000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1912500000000001</v>
+        <v>-0.19125</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.47125000000001</v>
+        <v>-22.74000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1725</v>
+        <v>-0.29625</v>
       </c>
       <c r="N6" t="n">
-        <v>-18.62125000000001</v>
+        <v>-23.0575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2812500000000001</v>
+        <v>-0.30875</v>
       </c>
       <c r="N7" t="n">
-        <v>-17.13500000000001</v>
+        <v>-19.12875000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.25375</v>
+        <v>-0.3025</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.51000000000001</v>
+        <v>-13.91000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>-0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2475000000000001</v>
+        <v>-0.2475</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.795000000000009</v>
+        <v>-4.795000000000007</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.01</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2475000000000001</v>
+        <v>-0.2475</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.045000000000009</v>
+        <v>-4.045000000000007</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>-0.06</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2800000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.443750000000009</v>
+        <v>-5.443750000000008</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>-0.15</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2812500000000001</v>
+        <v>-0.28125</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.076250000000008</v>
+        <v>-4.076250000000007</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
         <v>-0.37</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1875000000000001</v>
+        <v>-0.1875</v>
       </c>
       <c r="N13" t="n">
-        <v>5.987499999999992</v>
+        <v>5.987499999999993</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2434</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" t="n">
+        <v>24</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-53.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-149.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-13.26750000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-27.2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.037376048817697</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-42.15000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>3.740017746228927</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
